--- a/baseline_code/Data/Plane_data.xlsx
+++ b/baseline_code/Data/Plane_data.xlsx
@@ -1,42 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jens/Documents/Master/Master Q3/Agent Based Modeling/agent-based-modelling/baseline_code/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A904A56-30AF-3943-A198-596E29BD584D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="1180" windowWidth="18340" windowHeight="20940" xr2:uid="{21661984-882B-F040-AD8A-DFBE66DF4774}"/>
+    <workbookView xWindow="760" yWindow="1180" windowWidth="18340" windowHeight="20940"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>Plane</t>
   </si>
@@ -50,44 +28,89 @@
     <t>KL642</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>BA441</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>LH997</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>AF1341</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
     <t>EK149</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>U28672</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>TK1954</t>
   </si>
   <si>
+    <t>200</t>
+  </si>
+  <si>
     <t>SK553</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>OS374</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>IB3171</t>
+  </si>
+  <si>
+    <t>280</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -445,11 +468,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEABDABD-8917-EA45-BF9B-5ABDE3A5CCE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -460,114 +483,114 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>9</v>
-      </c>
-      <c r="C9">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>555</v>
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_code/Data/Plane_data.xlsx
+++ b/baseline_code/Data/Plane_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
   <si>
     <t>Plane</t>
   </si>
@@ -25,6 +25,12 @@
     <t>SIBT</t>
   </si>
   <si>
+    <t>Cargo From</t>
+  </si>
+  <si>
+    <t>Cargo To</t>
+  </si>
+  <si>
     <t>KL642</t>
   </si>
   <si>
@@ -34,12 +40,21 @@
     <t>120</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>BA441</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>LH997</t>
   </si>
   <si>
@@ -47,6 +62,9 @@
   </si>
   <si>
     <t>150</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>AF1341</t>
@@ -469,10 +487,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -482,115 +500,181 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
+      <c r="E11" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_code/Data/Plane_data.xlsx
+++ b/baseline_code/Data/Plane_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
   <si>
     <t>Plane</t>
   </si>
@@ -43,6 +43,11 @@
     <t>1</t>
   </si>
   <si>
+    <r>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
     <t>BA441</t>
   </si>
   <si>
@@ -61,7 +66,14 @@
     <t>9</t>
   </si>
   <si>
-    <t>150</t>
+    <r>
+      <t>15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
   </si>
   <si>
     <t>4</t>
@@ -521,157 +533,157 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
